--- a/Result/profitability/8227.xlsx
+++ b/Result/profitability/8227.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM48"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4424999999999999</v>
+        <v>0.75375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.9325</v>
+        <v>21.7175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0.335</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>23.025</v>
+        <v>21.50375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.19625</v>
+        <v>0.49625</v>
       </c>
       <c r="N4" t="n">
-        <v>23.555</v>
+        <v>23.36</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.58</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1</v>
+        <v>0.43125</v>
       </c>
       <c r="N5" t="n">
-        <v>24.845</v>
+        <v>23.69125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.18625</v>
+        <v>0.3525</v>
       </c>
       <c r="N6" t="n">
-        <v>25.92875</v>
+        <v>25.655</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05875000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
-        <v>27.0275</v>
+        <v>27.2175</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -6524,6 +6524,133 @@
       </c>
       <c r="AM48" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8227</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>613</v>
+      </c>
+      <c r="D49" t="n">
+        <v>508</v>
+      </c>
+      <c r="E49" t="n">
+        <v>105</v>
+      </c>
+      <c r="F49" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>7.56%</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>67</v>
+      </c>
+      <c r="J49" t="n">
+        <v>113</v>
+      </c>
+      <c r="K49" t="n">
+        <v>103</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.76125</v>
+      </c>
+      <c r="N49" t="n">
+        <v>22.47375</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.046875</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-0.09533898305084754</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-44.16666666666666</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>-9.23</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>-0.3508171797795515</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
